--- a/output/pdf_financials_xlsx/KEY.xlsx
+++ b/output/pdf_financials_xlsx/KEY.xlsx
@@ -3215,7 +3215,7 @@
         <v>0</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>14.977</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>14.977</v>
@@ -3224,43 +3224,43 @@
         <v>0</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.518</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>11.309</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>13.447</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>16.477</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>326.381</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>326.381</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>2.901</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>15.94</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>20.088</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>118.441</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>2331.518</v>
       </c>
     </row>
     <row r="35">
@@ -3331,7 +3331,7 @@
         <v>0</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>14.977</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>14.977</v>
@@ -3340,43 +3340,43 @@
         <v>0</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.518</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>11.309</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>13.447</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>16.477</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>326.381</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>326.381</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>2.901</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>15.94</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>20.088</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>118.441</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>2331.518</v>
       </c>
     </row>
     <row r="37">
@@ -4036,43 +4036,43 @@
         <v>237.888</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>54.723</v>
+        <v>54.205</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>94.453</v>
+        <v>83.14400000000001</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>69.169</v>
+        <v>55.722</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>107.09</v>
+        <v>90.613</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>354.546</v>
+        <v>28.165</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>354.546</v>
+        <v>28.165</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>80.39700000000001</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>36.304</v>
+        <v>33.403</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>67.97199999999999</v>
+        <v>52.032</v>
       </c>
       <c r="O48" s="3" t="n">
         <v>98.468</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>153.986</v>
+        <v>133.898</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>221.837</v>
+        <v>103.396</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>4445.713</v>
+        <v>2114.195</v>
       </c>
     </row>
     <row r="49">
@@ -5289,7 +5289,7 @@
         <v>0</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>0</v>
+        <v>52.5</v>
       </c>
       <c r="F69" s="3" t="n">
         <v>0</v>
@@ -5405,7 +5405,7 @@
         <v>0</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0</v>
+        <v>52.5</v>
       </c>
       <c r="F71" s="3" t="n">
         <v>0</v>
@@ -5637,7 +5637,7 @@
         <v>116.156</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>450.26</v>
+        <v>397.76</v>
       </c>
       <c r="F75" s="3" t="n">
         <v>115.74</v>
@@ -5753,7 +5753,7 @@
         <v>478.364</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>672.1660000000001</v>
+        <v>619.6660000000001</v>
       </c>
       <c r="F77" s="3" t="n">
         <v>1239.332</v>
@@ -5869,7 +5869,7 @@
         <v>478.364</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>672.1660000000001</v>
+        <v>619.6660000000001</v>
       </c>
       <c r="F79" s="3" t="n">
         <v>1239.332</v>
@@ -6217,7 +6217,7 @@
         <v>574.248</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>478.013</v>
+        <v>530.513</v>
       </c>
       <c r="F85" s="3" t="n">
         <v>0</v>
@@ -8614,28 +8614,28 @@
         </is>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-1.439</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>-126.019</v>
+        <v>-178.666</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>-137.893</v>
+        <v>-187.309</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-44.645</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>-60</v>
+        <v>-103.566</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>-30</v>
+        <v>-77.261</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>-192.648</v>
+        <v>-245.452</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>-317.26</v>
+        <v>-372.698</v>
       </c>
     </row>
     <row r="125">
@@ -8678,28 +8678,28 @@
         </is>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-1.439</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>-126.019</v>
+        <v>-178.666</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>-137.893</v>
+        <v>-187.309</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-44.645</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>-60</v>
+        <v>-103.566</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>-30</v>
+        <v>-77.261</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>-192.648</v>
+        <v>-245.452</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>-317.26</v>
+        <v>-372.698</v>
       </c>
     </row>
     <row r="126">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -18649,7 +18649,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -33342,7 +33342,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -38752,7 +38752,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>LongTermDebt</t>
+          <t>CurrentDebt</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -44768,7 +44768,7 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -52635,7 +52635,11 @@
           <t>Lease payments 16,30</t>
         </is>
       </c>
-      <c r="D442" t="inlineStr"/>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E442" t="inlineStr">
         <is>
           <t>-</t>
@@ -54685,7 +54689,11 @@
           <t>Lease payments 15, 29</t>
         </is>
       </c>
-      <c r="D464" t="inlineStr"/>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E464" t="inlineStr">
         <is>
           <t>-</t>
@@ -59181,7 +59189,11 @@
           <t>Lease payments 17, 31</t>
         </is>
       </c>
-      <c r="D510" t="inlineStr"/>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E510" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/KEY.xlsx
+++ b/output/pdf_financials_xlsx/KEY.xlsx
@@ -7846,25 +7846,25 @@
         </is>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>23.946</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>0.499</v>
       </c>
       <c r="M112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>0</v>
+        <v>18.191</v>
       </c>
       <c r="O112" s="3" t="n">
-        <v>0</v>
+        <v>39.815</v>
       </c>
       <c r="P112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q112" s="3" t="n">
-        <v>0</v>
+        <v>5.705</v>
       </c>
       <c r="R112" s="3" t="n">
         <v>0</v>
@@ -51855,7 +51855,11 @@
           <t>Proceeds on disposal of property, plant and equipment 9</t>
         </is>
       </c>
-      <c r="D434" t="inlineStr"/>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E434" t="inlineStr">
         <is>
           <t>-</t>
@@ -58286,7 +58290,11 @@
           <t>Proceeds on disposal of property, plant, and equipment 11</t>
         </is>
       </c>
-      <c r="D501" t="inlineStr"/>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E501" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/KEY.xlsx
+++ b/output/pdf_financials_xlsx/KEY.xlsx
@@ -2330,20 +2330,14 @@
       <c r="G23" s="3" t="n">
         <v>229.989</v>
       </c>
-      <c r="H23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H23" s="3" t="n">
+        <v>201.92</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>216.851</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>289.92</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>402.828</v>
@@ -6998,20 +6992,14 @@
       <c r="G99" s="3" t="n">
         <v>229.989</v>
       </c>
-      <c r="H99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H99" s="3" t="n">
+        <v>201.92</v>
+      </c>
+      <c r="I99" s="3" t="n">
+        <v>216.851</v>
+      </c>
+      <c r="J99" s="3" t="n">
+        <v>289.92</v>
       </c>
       <c r="K99" s="3" t="n">
         <v>402.828</v>
@@ -7048,34 +7036,28 @@
         <v>42.07</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>44.955</v>
+        <v>53.342</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>61.051</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>88.782</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>102.425</v>
       </c>
       <c r="G100" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K100" s="3" t="n">
         <v>0</v>
@@ -7126,20 +7108,14 @@
       <c r="G101" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K101" s="3" t="n">
         <v>0</v>
@@ -7190,20 +7166,14 @@
       <c r="G102" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K102" s="3" t="n">
         <v>0</v>
@@ -7254,20 +7224,14 @@
       <c r="G103" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K103" s="3" t="n">
         <v>0</v>
@@ -7318,20 +7282,14 @@
       <c r="G104" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K104" s="3" t="n">
         <v>0</v>
@@ -7382,20 +7340,14 @@
       <c r="G105" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K105" s="3" t="n">
         <v>0</v>
@@ -7446,20 +7398,14 @@
       <c r="G106" s="3" t="n">
         <v>-79.502</v>
       </c>
-      <c r="H106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H106" s="3" t="n">
+        <v>65.672</v>
+      </c>
+      <c r="I106" s="3" t="n">
+        <v>-129.224</v>
+      </c>
+      <c r="J106" s="3" t="n">
+        <v>-53.942</v>
       </c>
       <c r="K106" s="3" t="n">
         <v>-91.96899999999999</v>
@@ -7510,20 +7456,14 @@
       <c r="G107" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K107" s="3" t="n">
         <v>0</v>
@@ -7574,20 +7514,14 @@
       <c r="G108" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K108" s="3" t="n">
         <v>0</v>
@@ -7638,20 +7572,14 @@
       <c r="G109" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K109" s="3" t="n">
         <v>0</v>
@@ -7685,10 +7613,10 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>3.362</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>5.019</v>
       </c>
       <c r="D110" s="3" t="n">
         <v>0</v>
@@ -7702,20 +7630,14 @@
       <c r="G110" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K110" s="3" t="n">
         <v>0</v>
@@ -7766,20 +7688,14 @@
       <c r="G111" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K111" s="3" t="n">
         <v>0</v>
@@ -7830,20 +7746,14 @@
       <c r="G112" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" s="3" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="J112" s="3" t="n">
+        <v>6.015</v>
       </c>
       <c r="K112" s="3" t="n">
         <v>23.946</v>
@@ -7894,20 +7804,14 @@
       <c r="G113" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K113" s="3" t="n">
         <v>0</v>
@@ -7958,20 +7862,14 @@
       <c r="G114" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K114" s="3" t="n">
         <v>0</v>
@@ -8022,20 +7920,14 @@
       <c r="G115" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K115" s="3" t="n">
         <v>0</v>
@@ -8086,20 +7978,14 @@
       <c r="G116" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K116" s="3" t="n">
         <v>0</v>
@@ -8150,20 +8036,14 @@
       <c r="G117" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K117" s="3" t="n">
         <v>0</v>
@@ -8214,20 +8094,14 @@
       <c r="G118" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K118" s="3" t="n">
         <v>0</v>
@@ -8278,20 +8152,14 @@
       <c r="G119" s="3" t="n">
         <v>-966.837</v>
       </c>
-      <c r="H119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H119" s="3" t="n">
+        <v>-757.4160000000001</v>
+      </c>
+      <c r="I119" s="3" t="n">
+        <v>-760.974</v>
+      </c>
+      <c r="J119" s="3" t="n">
+        <v>-646.9349999999999</v>
       </c>
       <c r="K119" s="3" t="n">
         <v>-1258.968</v>
@@ -8342,20 +8210,14 @@
       <c r="G120" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K120" s="3" t="n">
         <v>0</v>
@@ -8406,20 +8268,14 @@
       <c r="G121" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K121" s="3" t="n">
         <v>0</v>
@@ -8470,20 +8326,14 @@
       <c r="G122" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K122" s="3" t="n">
         <v>0</v>
@@ -8534,20 +8384,14 @@
       <c r="G123" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K123" s="3" t="n">
         <v>0</v>
@@ -8598,20 +8442,14 @@
       <c r="G124" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H124" s="3" t="n">
+        <v>-49.799</v>
+      </c>
+      <c r="I124" s="3" t="n">
+        <v>-97.73999999999999</v>
+      </c>
+      <c r="J124" s="3" t="n">
+        <v>-60</v>
       </c>
       <c r="K124" s="3" t="n">
         <v>-1.439</v>
@@ -8662,20 +8500,14 @@
       <c r="G125" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H125" s="3" t="n">
+        <v>-49.799</v>
+      </c>
+      <c r="I125" s="3" t="n">
+        <v>-97.73999999999999</v>
+      </c>
+      <c r="J125" s="3" t="n">
+        <v>-60</v>
       </c>
       <c r="K125" s="3" t="n">
         <v>-1.439</v>
@@ -8726,20 +8558,14 @@
       <c r="G126" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K126" s="3" t="n">
         <v>0</v>
@@ -8882,20 +8708,14 @@
       <c r="G128" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K128" s="3" t="n">
         <v>0</v>
@@ -8946,20 +8766,14 @@
       <c r="G129" s="3" t="n">
         <v>326.549</v>
       </c>
-      <c r="H129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H129" s="3" t="n">
+        <v>109.692</v>
+      </c>
+      <c r="I129" s="3" t="n">
+        <v>350.516</v>
+      </c>
+      <c r="J129" s="3" t="n">
+        <v>445.846</v>
       </c>
       <c r="K129" s="3" t="n">
         <v>314.912</v>
@@ -9010,20 +8824,14 @@
       <c r="G130" s="3" t="n">
         <v>186.651</v>
       </c>
-      <c r="H130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H130" s="3" t="n">
+        <v>11.309</v>
+      </c>
+      <c r="I130" s="3" t="n">
+        <v>13.447</v>
+      </c>
+      <c r="J130" s="3" t="n">
+        <v>16.477</v>
       </c>
       <c r="K130" s="3" t="n">
         <v>326.381</v>
@@ -9074,20 +8882,14 @@
       <c r="G131" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K131" s="3" t="n">
         <v>0</v>
@@ -9138,20 +8940,14 @@
       <c r="G132" s="3" t="n">
         <v>-175.342</v>
       </c>
-      <c r="H132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H132" s="3" t="n">
+        <v>2.138</v>
+      </c>
+      <c r="I132" s="3" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="J132" s="3" t="n">
+        <v>309.904</v>
       </c>
       <c r="K132" s="3" t="n">
         <v>-337.241</v>
@@ -9202,20 +8998,14 @@
       <c r="G133" s="3" t="n">
         <v>11.309</v>
       </c>
-      <c r="H133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H133" s="3" t="n">
+        <v>13.447</v>
+      </c>
+      <c r="I133" s="3" t="n">
+        <v>16.477</v>
+      </c>
+      <c r="J133" s="3" t="n">
+        <v>326.381</v>
       </c>
       <c r="K133" s="3" t="n">
         <v>-10.86</v>
@@ -9266,20 +9056,14 @@
       <c r="G134" s="3" t="n">
         <v>-786.795</v>
       </c>
-      <c r="H134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H134" s="3" t="n">
+        <v>-706.258</v>
+      </c>
+      <c r="I134" s="3" t="n">
+        <v>-567.042</v>
+      </c>
+      <c r="J134" s="3" t="n">
+        <v>-698.992</v>
       </c>
       <c r="K134" s="3" t="n">
         <v>-987.317</v>
@@ -9330,20 +9114,14 @@
       <c r="G135" s="3" t="n">
         <v>-326.201</v>
       </c>
-      <c r="H135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H135" s="3" t="n">
+        <v>-58.103</v>
+      </c>
+      <c r="I135" s="3" t="n">
+        <v>-154.116</v>
+      </c>
+      <c r="J135" s="3" t="n">
+        <v>-185.295</v>
       </c>
       <c r="K135" s="3" t="n">
         <v>-382.988</v>
@@ -9381,7 +9159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U603"/>
+  <dimension ref="A1:U627"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -50540,10 +50318,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M420" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M420" s="5" t="n">
+        <v>289.92</v>
       </c>
       <c r="N420" s="5" t="n">
         <v>402.828</v>
@@ -50919,15 +50695,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L424" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M424" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L424" s="5" t="n">
+        <v>-28.323</v>
+      </c>
+      <c r="M424" s="5" t="n">
+        <v>-31.171</v>
       </c>
       <c r="N424" t="inlineStr">
         <is>
@@ -51067,7 +50839,11 @@
           <t>Deferred income tax expense 18</t>
         </is>
       </c>
-      <c r="D426" t="inlineStr"/>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E426" t="inlineStr">
         <is>
           <t>-</t>
@@ -51393,25 +51169,17 @@
       <c r="J429" s="5" t="n">
         <v>-6.041</v>
       </c>
-      <c r="K429" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L429" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M429" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N429" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K429" s="5" t="n">
+        <v>-7.003</v>
+      </c>
+      <c r="L429" s="5" t="n">
+        <v>-4.249</v>
+      </c>
+      <c r="M429" s="5" t="n">
+        <v>-10.79</v>
+      </c>
+      <c r="N429" s="5" t="n">
+        <v>-9.753</v>
       </c>
       <c r="O429" t="inlineStr">
         <is>
@@ -52084,20 +51852,14 @@
       <c r="J436" s="5" t="n">
         <v>-966.837</v>
       </c>
-      <c r="K436" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L436" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M436" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K436" s="5" t="n">
+        <v>-757.4160000000001</v>
+      </c>
+      <c r="L436" s="5" t="n">
+        <v>-760.974</v>
+      </c>
+      <c r="M436" s="5" t="n">
+        <v>-646.9349999999999</v>
       </c>
       <c r="N436" s="5" t="n">
         <v>-1258.968</v>
@@ -52965,20 +52727,14 @@
       <c r="J445" s="5" t="n">
         <v>4.352</v>
       </c>
-      <c r="K445" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L445" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M445" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K445" s="5" t="n">
+        <v>1.707</v>
+      </c>
+      <c r="L445" s="5" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="M445" s="5" t="n">
+        <v>-2.704</v>
       </c>
       <c r="N445" s="5" t="n">
         <v>2.486</v>
@@ -53052,20 +52808,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L446" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M446" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K446" s="5" t="n">
+        <v>2.138</v>
+      </c>
+      <c r="L446" s="5" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="M446" s="5" t="n">
+        <v>309.904</v>
       </c>
       <c r="N446" t="inlineStr">
         <is>
@@ -53148,30 +52898,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J447" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K447" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L447" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M447" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N447" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J447" s="5" t="n">
+        <v>186.651</v>
+      </c>
+      <c r="K447" s="5" t="n">
+        <v>11.309</v>
+      </c>
+      <c r="L447" s="5" t="n">
+        <v>13.447</v>
+      </c>
+      <c r="M447" s="5" t="n">
+        <v>16.477</v>
+      </c>
+      <c r="N447" s="5" t="n">
+        <v>326.381</v>
       </c>
       <c r="O447" t="inlineStr">
         <is>
@@ -53245,25 +52985,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J448" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K448" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L448" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M448" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J448" s="5" t="n">
+        <v>11.309</v>
+      </c>
+      <c r="K448" s="5" t="n">
+        <v>13.447</v>
+      </c>
+      <c r="L448" s="5" t="n">
+        <v>16.477</v>
+      </c>
+      <c r="M448" s="5" t="n">
+        <v>326.381</v>
       </c>
       <c r="N448" t="inlineStr">
         <is>
@@ -53426,20 +53158,14 @@
       <c r="J450" s="5" t="n">
         <v>61.27</v>
       </c>
-      <c r="K450" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L450" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M450" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K450" s="5" t="n">
+        <v>74.383</v>
+      </c>
+      <c r="L450" s="5" t="n">
+        <v>84.134</v>
+      </c>
+      <c r="M450" s="5" t="n">
+        <v>82.996</v>
       </c>
       <c r="N450" s="5" t="n">
         <v>94.026</v>
@@ -53505,25 +53231,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L451" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M451" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N451" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K451" s="5" t="n">
+        <v>10.93</v>
+      </c>
+      <c r="L451" s="5" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="M451" s="5" t="n">
+        <v>14.039</v>
+      </c>
+      <c r="N451" s="5" t="n">
+        <v>13.695</v>
       </c>
       <c r="O451" t="inlineStr">
         <is>
@@ -53598,25 +53316,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L452" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M452" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N452" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K452" s="5" t="n">
+        <v>169.318</v>
+      </c>
+      <c r="L452" s="5" t="n">
+        <v>171.615</v>
+      </c>
+      <c r="M452" s="5" t="n">
+        <v>165.978</v>
+      </c>
+      <c r="N452" s="5" t="n">
+        <v>206.719</v>
       </c>
       <c r="O452" t="inlineStr">
         <is>
@@ -53691,15 +53401,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L453" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K453" s="5" t="n">
+        <v>-31.231</v>
+      </c>
+      <c r="L453" s="5" t="n">
+        <v>68.93000000000001</v>
       </c>
       <c r="M453" t="inlineStr">
         <is>
@@ -53759,7 +53465,11 @@
           <t>Deferred income tax expense 17</t>
         </is>
       </c>
-      <c r="D454" t="inlineStr"/>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E454" t="inlineStr">
         <is>
           <t>-</t>
@@ -53786,25 +53496,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L454" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M454" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N454" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K454" s="5" t="n">
+        <v>11.791</v>
+      </c>
+      <c r="L454" s="5" t="n">
+        <v>75.10599999999999</v>
+      </c>
+      <c r="M454" s="5" t="n">
+        <v>99.383</v>
+      </c>
+      <c r="N454" s="5" t="n">
+        <v>99.11199999999999</v>
       </c>
       <c r="O454" t="inlineStr">
         <is>
@@ -53884,15 +53586,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L455" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M455" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L455" s="5" t="n">
+        <v>-4.249</v>
+      </c>
+      <c r="M455" s="5" t="n">
+        <v>-10.79</v>
       </c>
       <c r="N455" t="inlineStr">
         <is>
@@ -53968,25 +53666,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L456" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M456" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N456" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K456" s="5" t="n">
+        <v>65.672</v>
+      </c>
+      <c r="L456" s="5" t="n">
+        <v>-129.224</v>
+      </c>
+      <c r="M456" s="5" t="n">
+        <v>-53.942</v>
+      </c>
+      <c r="N456" s="5" t="n">
+        <v>-106.231</v>
       </c>
       <c r="O456" t="inlineStr">
         <is>
@@ -54057,25 +53747,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K457" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L457" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M457" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N457" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K457" s="5" t="n">
+        <v>-29.992</v>
+      </c>
+      <c r="L457" s="5" t="n">
+        <v>-3.642</v>
+      </c>
+      <c r="M457" s="5" t="n">
+        <v>107.164</v>
+      </c>
+      <c r="N457" s="5" t="n">
+        <v>37.607</v>
       </c>
       <c r="O457" t="inlineStr">
         <is>
@@ -54618,10 +54300,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J463" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J463" s="5" t="n">
+        <v>-12.833</v>
       </c>
       <c r="K463" t="inlineStr">
         <is>
@@ -54815,25 +54495,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K465" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L465" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M465" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N465" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K465" s="5" t="n">
+        <v>-237.355</v>
+      </c>
+      <c r="L465" s="5" t="n">
+        <v>-274.438</v>
+      </c>
+      <c r="M465" s="5" t="n">
+        <v>-308.609</v>
+      </c>
+      <c r="N465" s="5" t="n">
+        <v>-356.334</v>
       </c>
       <c r="O465" t="inlineStr">
         <is>
@@ -55296,15 +54968,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K470" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L470" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K470" s="5" t="n">
+        <v>95.517</v>
+      </c>
+      <c r="L470" s="5" t="n">
+        <v>-28.323</v>
       </c>
       <c r="M470" t="inlineStr">
         <is>
@@ -55581,20 +55249,14 @@
       <c r="J473" s="5" t="n">
         <v>460.594</v>
       </c>
-      <c r="K473" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L473" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M473" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K473" s="5" t="n">
+        <v>648.155</v>
+      </c>
+      <c r="L473" s="5" t="n">
+        <v>412.926</v>
+      </c>
+      <c r="M473" s="5" t="n">
+        <v>513.697</v>
       </c>
       <c r="N473" s="5" t="n">
         <v>604.329</v>
@@ -55772,15 +55434,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L475" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M475" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L475" s="5" t="n">
+        <v>344.871</v>
+      </c>
+      <c r="M475" s="5" t="n">
+        <v>493.856</v>
       </c>
       <c r="N475" t="inlineStr">
         <is>
@@ -55871,10 +55529,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L476" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L476" s="5" t="n">
+        <v>-14.528</v>
       </c>
       <c r="M476" t="inlineStr">
         <is>
@@ -55960,15 +55616,11 @@
       <c r="I477" s="5" t="n">
         <v>186.133</v>
       </c>
-      <c r="J477" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K477" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J477" s="5" t="n">
+        <v>-175.342</v>
+      </c>
+      <c r="K477" s="5" t="n">
+        <v>2.138</v>
       </c>
       <c r="L477" t="inlineStr">
         <is>
@@ -56256,15 +55908,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M480" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N480" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M480" s="5" t="n">
+        <v>25.99</v>
+      </c>
+      <c r="N480" s="5" t="n">
+        <v>-111.165</v>
       </c>
       <c r="O480" t="inlineStr">
         <is>
@@ -56347,15 +55995,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M481" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N481" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M481" s="5" t="n">
+        <v>-31.171</v>
+      </c>
+      <c r="N481" s="5" t="n">
+        <v>34.977</v>
       </c>
       <c r="O481" t="inlineStr">
         <is>
@@ -56541,15 +56185,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M483" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N483" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M483" s="5" t="n">
+        <v>309.904</v>
+      </c>
+      <c r="N483" s="5" t="n">
+        <v>-337.241</v>
       </c>
       <c r="O483" t="inlineStr">
         <is>
@@ -56644,15 +56284,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M484" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N484" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M484" s="5" t="n">
+        <v>326.381</v>
+      </c>
+      <c r="N484" s="5" t="n">
+        <v>-10.86</v>
       </c>
       <c r="O484" t="inlineStr">
         <is>
@@ -57026,25 +56662,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L488" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M488" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N488" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K488" s="5" t="n">
+        <v>118.854</v>
+      </c>
+      <c r="L488" s="5" t="n">
+        <v>169.777</v>
+      </c>
+      <c r="M488" s="5" t="n">
+        <v>181.118</v>
+      </c>
+      <c r="N488" s="5" t="n">
+        <v>196.419</v>
       </c>
       <c r="O488" t="inlineStr">
         <is>
@@ -57735,10 +57363,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M495" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M495" s="5" t="n">
+        <v>20.83</v>
       </c>
       <c r="N495" s="5" t="n">
         <v>56.911</v>
@@ -58129,10 +57755,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M499" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M499" s="5" t="n">
+        <v>-61.122</v>
       </c>
       <c r="N499" s="5" t="n">
         <v>-333.204</v>
@@ -58232,10 +57856,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M500" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M500" s="5" t="n">
+        <v>-698.992</v>
       </c>
       <c r="N500" s="5" t="n">
         <v>-987.317</v>
@@ -58335,10 +57957,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M501" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M501" s="5" t="n">
+        <v>6.015</v>
       </c>
       <c r="N501" s="5" t="n">
         <v>23.946</v>
@@ -59428,20 +59048,16 @@
       <c r="J512" s="5" t="n">
         <v>326.549</v>
       </c>
-      <c r="K512" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K512" s="5" t="n">
+        <v>109.692</v>
       </c>
       <c r="L512" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M512" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M512" s="5" t="n">
+        <v>445.846</v>
       </c>
       <c r="N512" s="5" t="n">
         <v>314.912</v>
@@ -59517,20 +59133,14 @@
       <c r="J513" s="5" t="n">
         <v>2.54</v>
       </c>
-      <c r="K513" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L513" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M513" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K513" s="5" t="n">
+        <v>61.492</v>
+      </c>
+      <c r="L513" s="5" t="n">
+        <v>73.348</v>
+      </c>
+      <c r="M513" s="5" t="n">
+        <v>3.351</v>
       </c>
       <c r="N513" s="5" t="n">
         <v>0.353</v>
@@ -59582,7 +59192,7 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Finance costs 25</t>
+          <t>Long-term incentive plan expense 21</t>
         </is>
       </c>
       <c r="D514" t="inlineStr"/>
@@ -59591,46 +59201,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F514" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G514" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H514" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F514" s="5" t="n">
+        <v>18.225</v>
+      </c>
+      <c r="G514" s="5" t="n">
+        <v>26.422</v>
+      </c>
+      <c r="H514" s="5" t="n">
+        <v>10.233</v>
       </c>
       <c r="I514" s="5" t="n">
-        <v>10.566</v>
-      </c>
-      <c r="J514" s="5" t="n">
-        <v>10.705</v>
-      </c>
-      <c r="K514" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L514" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M514" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N514" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>28.297</v>
+      </c>
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K514" s="5" t="n">
+        <v>32.146</v>
+      </c>
+      <c r="L514" s="5" t="n">
+        <v>16.84</v>
+      </c>
+      <c r="M514" s="5" t="n">
+        <v>13.907</v>
+      </c>
+      <c r="N514" s="5" t="n">
+        <v>14.262</v>
       </c>
       <c r="O514" t="inlineStr">
         <is>
@@ -59681,7 +59279,7 @@
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>Depreciation, depletion and amortization expenses 26</t>
+          <t>Gain on disposal of property, plant and equipment 11</t>
         </is>
       </c>
       <c r="D515" t="inlineStr"/>
@@ -59705,11 +59303,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I515" s="5" t="n">
-        <v>102.425</v>
-      </c>
-      <c r="J515" s="5" t="n">
-        <v>138.697</v>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K515" t="inlineStr">
         <is>
@@ -59721,10 +59323,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M515" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M515" s="5" t="n">
+        <v>-20.447</v>
       </c>
       <c r="N515" t="inlineStr">
         <is>
@@ -59780,7 +59380,7 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Long-term incentive plan expense 20</t>
+          <t>Loss on settlement of finance lease 16</t>
         </is>
       </c>
       <c r="D516" t="inlineStr"/>
@@ -59804,11 +59404,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I516" s="5" t="n">
-        <v>28.297</v>
-      </c>
-      <c r="J516" s="5" t="n">
-        <v>38.513</v>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K516" t="inlineStr">
         <is>
@@ -59825,10 +59429,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N516" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N516" s="5" t="n">
+        <v>0.286</v>
       </c>
       <c r="O516" t="inlineStr">
         <is>
@@ -59874,12 +59476,12 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Adjustments for items not affecting cash</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>Unrealized gain on derivative financial instruments 21</t>
+          <t>Borrowings under credit facility 14, 29</t>
         </is>
       </c>
       <c r="D517" t="inlineStr"/>
@@ -59903,11 +59505,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I517" s="5" t="n">
-        <v>-12.627</v>
-      </c>
-      <c r="J517" s="5" t="n">
-        <v>-114.329</v>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K517" t="inlineStr">
         <is>
@@ -59919,15 +59525,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M517" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N517" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M517" s="5" t="n">
+        <v>3268.802</v>
+      </c>
+      <c r="N517" s="5" t="n">
+        <v>720</v>
       </c>
       <c r="O517" t="inlineStr">
         <is>
@@ -59973,12 +59575,12 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>Adjustments for items not affecting cash</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>Unrealized loss on foreign exchange</t>
+          <t>Repayments under credit facility 14, 29</t>
         </is>
       </c>
       <c r="D518" t="inlineStr"/>
@@ -60002,11 +59604,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I518" s="5" t="n">
-        <v>23.285</v>
-      </c>
-      <c r="J518" s="5" t="n">
-        <v>40.156</v>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K518" t="inlineStr">
         <is>
@@ -60018,15 +59624,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M518" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N518" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M518" s="5" t="n">
+        <v>-3503.802</v>
+      </c>
+      <c r="N518" s="5" t="n">
+        <v>-640</v>
       </c>
       <c r="O518" t="inlineStr">
         <is>
@@ -60072,12 +59674,12 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>Adjustments for items not affecting cash</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Deferred income tax expense 16</t>
+          <t>Proceeds from issuance of long-term debt 14, 29</t>
         </is>
       </c>
       <c r="D519" t="inlineStr"/>
@@ -60101,11 +59703,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I519" s="5" t="n">
-        <v>59.649</v>
-      </c>
-      <c r="J519" s="5" t="n">
-        <v>61.524</v>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K519" t="inlineStr">
         <is>
@@ -60117,15 +59723,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M519" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N519" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M519" s="5" t="n">
+        <v>400</v>
+      </c>
+      <c r="N519" s="5" t="n">
+        <v>400</v>
       </c>
       <c r="O519" t="inlineStr">
         <is>
@@ -60171,12 +59773,12 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Adjustments for items not affecting cash</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>Inventory write-down 8</t>
+          <t>Financing costs related to credit facility/long-term debt 14, 29</t>
         </is>
       </c>
       <c r="D520" t="inlineStr"/>
@@ -60195,14 +59797,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H520" s="5" t="n">
-        <v>5.628</v>
-      </c>
-      <c r="I520" s="5" t="n">
-        <v>2.058</v>
-      </c>
-      <c r="J520" s="5" t="n">
-        <v>60.639</v>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K520" t="inlineStr">
         <is>
@@ -60214,15 +59822,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M520" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N520" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M520" s="5" t="n">
+        <v>-3.527</v>
+      </c>
+      <c r="N520" s="5" t="n">
+        <v>-3.318</v>
       </c>
       <c r="O520" t="inlineStr">
         <is>
@@ -60268,15 +59872,19 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Adjustments for items not affecting cash</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>Loss on disposal of property, plant and equipment 10</t>
-        </is>
-      </c>
-      <c r="D521" t="inlineStr"/>
+          <t>Repayment of long-term debt 14, 29</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E521" t="inlineStr">
         <is>
           <t>-</t>
@@ -60297,8 +59905,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I521" s="5" t="n">
-        <v>0.482</v>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J521" t="inlineStr">
         <is>
@@ -60315,10 +59925,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M521" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M521" s="5" t="n">
+        <v>-60</v>
       </c>
       <c r="N521" t="inlineStr">
         <is>
@@ -60369,12 +59977,12 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Adjustments for items not affecting cash</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>Impairment expense 10</t>
+          <t>Issuance costs related to equity offering and other 18</t>
         </is>
       </c>
       <c r="D522" t="inlineStr"/>
@@ -60383,20 +59991,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F522" s="5" t="n">
-        <v>22.43</v>
-      </c>
-      <c r="G522" s="5" t="n">
-        <v>-24.012</v>
-      </c>
-      <c r="H522" s="5" t="n">
-        <v>29.567</v>
-      </c>
-      <c r="I522" s="5" t="n">
-        <v>0.577</v>
-      </c>
-      <c r="J522" s="5" t="n">
-        <v>80.24299999999999</v>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K522" t="inlineStr">
         <is>
@@ -60408,15 +60026,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M522" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N522" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M522" s="5" t="n">
+        <v>-19.742</v>
+      </c>
+      <c r="N522" s="5" t="n">
+        <v>-0.416</v>
       </c>
       <c r="O522" t="inlineStr">
         <is>
@@ -60462,19 +60076,15 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Adjustments for items not affecting cash</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital 28</t>
-        </is>
-      </c>
-      <c r="D523" t="inlineStr">
-        <is>
-          <t>ChangeInWorkingCapital</t>
-        </is>
-      </c>
+          <t>Repayment of finance lease liabilities 16</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr"/>
       <c r="E523" t="inlineStr">
         <is>
           <t>-</t>
@@ -60495,31 +60105,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I523" s="5" t="n">
-        <v>27.013</v>
-      </c>
-      <c r="J523" s="5" t="n">
-        <v>-79.502</v>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K523" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L523" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M523" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N523" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L523" s="5" t="n">
+        <v>-0.188</v>
+      </c>
+      <c r="M523" s="5" t="n">
+        <v>-2.25</v>
+      </c>
+      <c r="N523" s="5" t="n">
+        <v>-1.439</v>
       </c>
       <c r="O523" t="inlineStr">
         <is>
@@ -60565,15 +60173,19 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>Acquisitions 10</t>
-        </is>
-      </c>
-      <c r="D524" t="inlineStr"/>
+          <t>Net earnings:</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E524" t="inlineStr">
         <is>
           <t>-</t>
@@ -60594,26 +60206,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I524" s="5" t="n">
-        <v>-31.878</v>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J524" s="5" t="n">
-        <v>-221.388</v>
-      </c>
-      <c r="K524" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L524" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M524" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>229.989</v>
+      </c>
+      <c r="K524" s="5" t="n">
+        <v>201.92</v>
+      </c>
+      <c r="L524" s="5" t="n">
+        <v>216.851</v>
+      </c>
+      <c r="M524" s="5" t="n">
+        <v>289.92</v>
       </c>
       <c r="N524" t="inlineStr">
         <is>
@@ -60664,53 +60272,49 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>Adjustments for items not affecting cash</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>Capital expenditures 10</t>
-        </is>
-      </c>
-      <c r="D525" t="inlineStr">
-        <is>
-          <t>CapitalExpenditure</t>
-        </is>
-      </c>
+          <t>Finance costs 25</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr"/>
       <c r="E525" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F525" s="5" t="n">
-        <v>-133.614</v>
-      </c>
-      <c r="G525" s="5" t="n">
-        <v>-170.78</v>
-      </c>
-      <c r="H525" s="5" t="n">
-        <v>-165.606</v>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I525" s="5" t="n">
-        <v>-339.512</v>
+        <v>10.566</v>
       </c>
       <c r="J525" s="5" t="n">
-        <v>-786.795</v>
-      </c>
-      <c r="K525" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L525" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M525" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>10.705</v>
+      </c>
+      <c r="K525" s="5" t="n">
+        <v>10.93</v>
+      </c>
+      <c r="L525" s="5" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="M525" s="5" t="n">
+        <v>14.039</v>
       </c>
       <c r="N525" t="inlineStr">
         <is>
@@ -60761,12 +60365,12 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>Adjustments for items not affecting cash</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Proceeds on sale of assets 10</t>
+          <t>Depreciation, depletion and amortization expenses 26</t>
         </is>
       </c>
       <c r="D526" t="inlineStr"/>
@@ -60780,8 +60384,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G526" s="5" t="n">
-        <v>0.142</v>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H526" t="inlineStr">
         <is>
@@ -60789,25 +60395,19 @@
         </is>
       </c>
       <c r="I526" s="5" t="n">
-        <v>9.811</v>
+        <v>102.425</v>
       </c>
       <c r="J526" s="5" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="K526" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L526" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M526" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>138.697</v>
+      </c>
+      <c r="K526" s="5" t="n">
+        <v>169.318</v>
+      </c>
+      <c r="L526" s="5" t="n">
+        <v>171.615</v>
+      </c>
+      <c r="M526" s="5" t="n">
+        <v>165.978</v>
       </c>
       <c r="N526" t="inlineStr">
         <is>
@@ -60858,19 +60458,15 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>Adjustments for items not affecting cash</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital 28</t>
-        </is>
-      </c>
-      <c r="D527" t="inlineStr">
-        <is>
-          <t>ChangeInWorkingCapital</t>
-        </is>
-      </c>
+          <t>Long-term incentive plan expense 20</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr"/>
       <c r="E527" t="inlineStr">
         <is>
           <t>-</t>
@@ -60892,25 +60488,19 @@
         </is>
       </c>
       <c r="I527" s="5" t="n">
-        <v>40.394</v>
+        <v>28.297</v>
       </c>
       <c r="J527" s="5" t="n">
-        <v>40.716</v>
-      </c>
-      <c r="K527" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L527" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M527" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>38.513</v>
+      </c>
+      <c r="K527" s="5" t="n">
+        <v>32.146</v>
+      </c>
+      <c r="L527" s="5" t="n">
+        <v>16.84</v>
+      </c>
+      <c r="M527" s="5" t="n">
+        <v>13.907</v>
       </c>
       <c r="N527" t="inlineStr">
         <is>
@@ -60961,12 +60551,12 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Adjustments for items not affecting cash</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>Borrowings under credit facilities 14</t>
+          <t>Unrealized loss on derivative financial instruments 21</t>
         </is>
       </c>
       <c r="D528" t="inlineStr"/>
@@ -60975,35 +60565,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F528" s="5" t="n">
-        <v>384</v>
-      </c>
-      <c r="G528" s="5" t="n">
-        <v>325</v>
-      </c>
-      <c r="H528" s="5" t="n">
-        <v>752</v>
-      </c>
-      <c r="I528" s="5" t="n">
-        <v>1350</v>
-      </c>
-      <c r="J528" s="5" t="n">
-        <v>250</v>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K528" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L528" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M528" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L528" s="5" t="n">
+        <v>68.93000000000001</v>
+      </c>
+      <c r="M528" s="5" t="n">
+        <v>25.99</v>
       </c>
       <c r="N528" t="inlineStr">
         <is>
@@ -61054,49 +60650,53 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Adjustments for items not affecting cash</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>Repayments under credit facilities 14</t>
-        </is>
-      </c>
-      <c r="D529" t="inlineStr"/>
+          <t>Deferred income tax expense 16</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E529" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F529" s="5" t="n">
-        <v>-303</v>
-      </c>
-      <c r="G529" s="5" t="n">
-        <v>-295</v>
-      </c>
-      <c r="H529" s="5" t="n">
-        <v>-858</v>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I529" s="5" t="n">
-        <v>-1485</v>
+        <v>59.649</v>
       </c>
       <c r="J529" s="5" t="n">
-        <v>-160</v>
-      </c>
-      <c r="K529" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L529" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M529" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>61.524</v>
+      </c>
+      <c r="K529" s="5" t="n">
+        <v>11.791</v>
+      </c>
+      <c r="L529" s="5" t="n">
+        <v>75.10599999999999</v>
+      </c>
+      <c r="M529" s="5" t="n">
+        <v>99.383</v>
       </c>
       <c r="N529" t="inlineStr">
         <is>
@@ -61147,12 +60747,12 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Adjustments for items not affecting cash</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of long-term debt 14</t>
+          <t>Impairment expense 10</t>
         </is>
       </c>
       <c r="D530" t="inlineStr"/>
@@ -61162,34 +60762,28 @@
         </is>
       </c>
       <c r="F530" s="5" t="n">
-        <v>154.099</v>
+        <v>22.43</v>
       </c>
       <c r="G530" s="5" t="n">
-        <v>70</v>
+        <v>-24.012</v>
       </c>
       <c r="H530" s="5" t="n">
-        <v>202.332</v>
+        <v>29.567</v>
       </c>
       <c r="I530" s="5" t="n">
-        <v>434.122</v>
+        <v>0.577</v>
       </c>
       <c r="J530" s="5" t="n">
-        <v>75</v>
-      </c>
-      <c r="K530" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L530" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M530" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>80.24299999999999</v>
+      </c>
+      <c r="K530" s="5" t="n">
+        <v>95.30500000000001</v>
+      </c>
+      <c r="L530" s="5" t="n">
+        <v>12.27</v>
+      </c>
+      <c r="M530" s="5" t="n">
+        <v>20.83</v>
       </c>
       <c r="N530" t="inlineStr">
         <is>
@@ -61240,12 +60834,12 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Adjustments for items not affecting cash</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>Financing costs related to long-term debt 14</t>
+          <t>(Gain) loss on disposal of property, plant and equipment 10</t>
         </is>
       </c>
       <c r="D531" t="inlineStr"/>
@@ -61254,35 +60848,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F531" s="5" t="n">
-        <v>-0.85</v>
-      </c>
-      <c r="G531" s="5" t="n">
-        <v>-0.144</v>
-      </c>
-      <c r="H531" s="5" t="n">
-        <v>-2.21</v>
-      </c>
-      <c r="I531" s="5" t="n">
-        <v>-1.923</v>
-      </c>
-      <c r="J531" s="5" t="n">
-        <v>-2.07</v>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K531" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L531" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M531" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L531" s="5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="M531" s="5" t="n">
+        <v>-20.447</v>
       </c>
       <c r="N531" t="inlineStr">
         <is>
@@ -61333,17 +60933,17 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Adjustments for items not affecting cash</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Repayment of long-term debt 14</t>
+          <t>Changes in non-cash working capital 28</t>
         </is>
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>RepaymentOfDebt</t>
+          <t>ChangeInWorkingCapital</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
@@ -61351,8 +60951,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F532" s="5" t="n">
-        <v>-52.5</v>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G532" t="inlineStr">
         <is>
@@ -61365,27 +60967,19 @@
         </is>
       </c>
       <c r="I532" s="5" t="n">
-        <v>-52.5</v>
-      </c>
-      <c r="J532" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K532" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L532" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M532" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>27.013</v>
+      </c>
+      <c r="J532" s="5" t="n">
+        <v>-79.502</v>
+      </c>
+      <c r="K532" s="5" t="n">
+        <v>65.672</v>
+      </c>
+      <c r="L532" s="5" t="n">
+        <v>-129.224</v>
+      </c>
+      <c r="M532" s="5" t="n">
+        <v>-53.942</v>
       </c>
       <c r="N532" t="inlineStr">
         <is>
@@ -61436,12 +61030,12 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>Repayment of convertible debenture</t>
+          <t>Acquisitions 10</t>
         </is>
       </c>
       <c r="D533" t="inlineStr"/>
@@ -61466,27 +61060,19 @@
         </is>
       </c>
       <c r="I533" s="5" t="n">
-        <v>-0.039</v>
-      </c>
-      <c r="J533" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K533" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L533" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M533" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-31.878</v>
+      </c>
+      <c r="J533" s="5" t="n">
+        <v>-221.388</v>
+      </c>
+      <c r="K533" s="5" t="n">
+        <v>-24.644</v>
+      </c>
+      <c r="L533" s="5" t="n">
+        <v>-190.375</v>
+      </c>
+      <c r="M533" s="5" t="n">
+        <v>-61.122</v>
       </c>
       <c r="N533" t="inlineStr">
         <is>
@@ -61537,57 +61123,47 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>Proceeds from equity offering 17</t>
-        </is>
-      </c>
-      <c r="D534" t="inlineStr"/>
+          <t>Capital expenditures 10</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>CapitalExpenditure</t>
+        </is>
+      </c>
       <c r="E534" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F534" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G534" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H534" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I534" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F534" s="5" t="n">
+        <v>-133.614</v>
+      </c>
+      <c r="G534" s="5" t="n">
+        <v>-170.78</v>
+      </c>
+      <c r="H534" s="5" t="n">
+        <v>-165.606</v>
+      </c>
+      <c r="I534" s="5" t="n">
+        <v>-339.512</v>
       </c>
       <c r="J534" s="5" t="n">
-        <v>318.047</v>
-      </c>
-      <c r="K534" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L534" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M534" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-786.795</v>
+      </c>
+      <c r="K534" s="5" t="n">
+        <v>-706.258</v>
+      </c>
+      <c r="L534" s="5" t="n">
+        <v>-567.042</v>
+      </c>
+      <c r="M534" s="5" t="n">
+        <v>-698.992</v>
       </c>
       <c r="N534" t="inlineStr">
         <is>
@@ -61638,15 +61214,19 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>Issuance costs related to equity offering 17</t>
-        </is>
-      </c>
-      <c r="D535" t="inlineStr"/>
+          <t>Proceeds on disposal of property, plant, and equipment 10</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E535" t="inlineStr">
         <is>
           <t>-</t>
@@ -61672,23 +61252,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J535" s="5" t="n">
-        <v>-12.833</v>
+      <c r="J535" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K535" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L535" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M535" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L535" s="5" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="M535" s="5" t="n">
+        <v>6.015</v>
       </c>
       <c r="N535" t="inlineStr">
         <is>
@@ -61739,15 +61317,19 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of shares related to DRIP 17</t>
-        </is>
-      </c>
-      <c r="D536" t="inlineStr"/>
+          <t>Changes in non-cash working capital 28</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E536" t="inlineStr">
         <is>
           <t>-</t>
@@ -61769,25 +61351,19 @@
         </is>
       </c>
       <c r="I536" s="5" t="n">
-        <v>52.064</v>
+        <v>40.394</v>
       </c>
       <c r="J536" s="5" t="n">
-        <v>63.304</v>
-      </c>
-      <c r="K536" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L536" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M536" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>40.716</v>
+      </c>
+      <c r="K536" s="5" t="n">
+        <v>-29.992</v>
+      </c>
+      <c r="L536" s="5" t="n">
+        <v>-3.642</v>
+      </c>
+      <c r="M536" s="5" t="n">
+        <v>107.164</v>
       </c>
       <c r="N536" t="inlineStr">
         <is>
@@ -61843,7 +61419,7 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Dividends paid to shareholders 19</t>
+          <t>Borrowings under credit facilities 13</t>
         </is>
       </c>
       <c r="D537" t="inlineStr"/>
@@ -61867,26 +61443,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I537" s="5" t="n">
-        <v>-175.307</v>
-      </c>
-      <c r="J537" s="5" t="n">
-        <v>-204.899</v>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J537" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K537" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L537" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M537" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L537" s="5" t="n">
+        <v>1397.406</v>
+      </c>
+      <c r="M537" s="5" t="n">
+        <v>3268.802</v>
       </c>
       <c r="N537" t="inlineStr">
         <is>
@@ -61942,7 +61518,7 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>Cash, at the start of the period</t>
+          <t>Repayments under credit facilities 13</t>
         </is>
       </c>
       <c r="D538" t="inlineStr"/>
@@ -61956,32 +61532,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G538" s="5" t="n">
-        <v>14.977</v>
-      </c>
-      <c r="H538" s="5" t="n">
-        <v>21.813</v>
-      </c>
-      <c r="I538" s="5" t="n">
-        <v>0.518</v>
-      </c>
-      <c r="J538" s="5" t="n">
-        <v>186.651</v>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K538" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L538" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M538" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L538" s="5" t="n">
+        <v>-1532.406</v>
+      </c>
+      <c r="M538" s="5" t="n">
+        <v>-3503.802</v>
       </c>
       <c r="N538" t="inlineStr">
         <is>
@@ -62037,14 +61617,10 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>Cash, at the end of the period</t>
-        </is>
-      </c>
-      <c r="D539" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>Proceeds from issuance of long-term debt 13</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr"/>
       <c r="E539" t="inlineStr">
         <is>
           <t>-</t>
@@ -62055,32 +61631,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G539" s="5" t="n">
-        <v>21.813</v>
-      </c>
-      <c r="H539" s="5" t="n">
-        <v>0.518</v>
-      </c>
-      <c r="I539" s="5" t="n">
-        <v>186.651</v>
-      </c>
-      <c r="J539" s="5" t="n">
-        <v>11.309</v>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K539" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L539" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M539" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L539" s="5" t="n">
+        <v>360</v>
+      </c>
+      <c r="M539" s="5" t="n">
+        <v>400</v>
       </c>
       <c r="N539" t="inlineStr">
         <is>
@@ -62131,12 +61711,12 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Adjustments for items not affecting cash</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>Depreciation and amortization expense 27</t>
+          <t>Financing costs related to credit facilities/long-term debt 13</t>
         </is>
       </c>
       <c r="D540" t="inlineStr"/>
@@ -62145,17 +61725,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F540" s="5" t="n">
-        <v>53.342</v>
-      </c>
-      <c r="G540" s="5" t="n">
-        <v>61.051</v>
-      </c>
-      <c r="H540" s="5" t="n">
-        <v>88.782</v>
-      </c>
-      <c r="I540" s="5" t="n">
-        <v>102.425</v>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J540" t="inlineStr">
         <is>
@@ -62167,15 +61755,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L540" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M540" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L540" s="5" t="n">
+        <v>-2.238</v>
+      </c>
+      <c r="M540" s="5" t="n">
+        <v>-3.527</v>
       </c>
       <c r="N540" t="inlineStr">
         <is>
@@ -62226,31 +61810,43 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Adjustments for items not affecting cash</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Long-term incentive plan expense 21</t>
-        </is>
-      </c>
-      <c r="D541" t="inlineStr"/>
+          <t>Repayment of long-term debt 13</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E541" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F541" s="5" t="n">
-        <v>18.225</v>
-      </c>
-      <c r="G541" s="5" t="n">
-        <v>26.422</v>
-      </c>
-      <c r="H541" s="5" t="n">
-        <v>10.233</v>
-      </c>
-      <c r="I541" s="5" t="n">
-        <v>28.297</v>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J541" t="inlineStr">
         <is>
@@ -62262,15 +61858,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L541" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M541" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L541" s="5" t="n">
+        <v>-97.73999999999999</v>
+      </c>
+      <c r="M541" s="5" t="n">
+        <v>-60</v>
       </c>
       <c r="N541" t="inlineStr">
         <is>
@@ -62321,12 +61913,12 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Business combination 6</t>
+          <t>Proceeds from equity offering 17</t>
         </is>
       </c>
       <c r="D542" t="inlineStr"/>
@@ -62345,33 +61937,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H542" s="5" t="n">
-        <v>-236.54</v>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I542" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J542" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J542" s="5" t="n">
+        <v>318.047</v>
       </c>
       <c r="K542" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L542" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M542" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L542" s="5" t="n">
+        <v>344.871</v>
+      </c>
+      <c r="M542" s="5" t="n">
+        <v>493.856</v>
       </c>
       <c r="N542" t="inlineStr">
         <is>
@@ -62422,12 +62010,12 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Asset acquisitions 10</t>
+          <t>Issuance costs related to equity offering 17</t>
         </is>
       </c>
       <c r="D543" t="inlineStr"/>
@@ -62446,31 +62034,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H543" s="5" t="n">
-        <v>-44.203</v>
-      </c>
-      <c r="I543" s="5" t="n">
-        <v>-31.878</v>
-      </c>
-      <c r="J543" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J543" s="5" t="n">
+        <v>-12.833</v>
       </c>
       <c r="K543" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L543" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M543" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L543" s="5" t="n">
+        <v>-14.528</v>
+      </c>
+      <c r="M543" s="5" t="n">
+        <v>-19.742</v>
       </c>
       <c r="N543" t="inlineStr">
         <is>
@@ -62526,7 +62112,7 @@
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>Repayment of convertible debenture 15</t>
+          <t>Proceeds from issuance of shares related to DRIP 17</t>
         </is>
       </c>
       <c r="D544" t="inlineStr"/>
@@ -62540,8 +62126,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G544" s="5" t="n">
-        <v>-0.043</v>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H544" t="inlineStr">
         <is>
@@ -62549,27 +62137,19 @@
         </is>
       </c>
       <c r="I544" s="5" t="n">
-        <v>-0.039</v>
-      </c>
-      <c r="J544" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K544" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L544" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M544" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>52.064</v>
+      </c>
+      <c r="J544" s="5" t="n">
+        <v>63.304</v>
+      </c>
+      <c r="K544" s="5" t="n">
+        <v>118.854</v>
+      </c>
+      <c r="L544" s="5" t="n">
+        <v>169.777</v>
+      </c>
+      <c r="M544" s="5" t="n">
+        <v>181.118</v>
       </c>
       <c r="N544" t="inlineStr">
         <is>
@@ -62620,19 +62200,15 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>Cash provided by (used in)</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>(Thousands of Canadian dollars, except share information) Note $ $ Net earnings</t>
-        </is>
-      </c>
-      <c r="D545" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+          <t>Repayment of finance lease liabilities 15</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr"/>
       <c r="E545" t="inlineStr">
         <is>
           <t>-</t>
@@ -62643,11 +62219,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G545" s="5" t="n">
-        <v>135.218</v>
-      </c>
-      <c r="H545" s="5" t="n">
-        <v>130.601</v>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I545" t="inlineStr">
         <is>
@@ -62664,15 +62244,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L545" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M545" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L545" s="5" t="n">
+        <v>-0.188</v>
+      </c>
+      <c r="M545" s="5" t="n">
+        <v>-2.25</v>
       </c>
       <c r="N545" t="inlineStr">
         <is>
@@ -62723,12 +62299,12 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>Adjustments for items not affecting cash</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>Operating revenues 30 2,942,277 2,569,158 Finance costs 26</t>
+          <t>Dividends paid to shareholders 19</t>
         </is>
       </c>
       <c r="D546" t="inlineStr"/>
@@ -62742,36 +62318,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G546" s="5" t="n">
-        <v>7.501</v>
-      </c>
-      <c r="H546" s="5" t="n">
-        <v>8.952999999999999</v>
-      </c>
-      <c r="I546" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J546" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K546" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L546" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M546" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I546" s="5" t="n">
+        <v>-175.307</v>
+      </c>
+      <c r="J546" s="5" t="n">
+        <v>-204.899</v>
+      </c>
+      <c r="K546" s="5" t="n">
+        <v>-237.355</v>
+      </c>
+      <c r="L546" s="5" t="n">
+        <v>-274.438</v>
+      </c>
+      <c r="M546" s="5" t="n">
+        <v>-308.609</v>
       </c>
       <c r="N546" t="inlineStr">
         <is>
@@ -62822,15 +62392,19 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>Adjustments for items not affecting cash</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Operating expenses 30 (2,581,374) (2,265,478) Depreciation and amortization expense 27</t>
-        </is>
-      </c>
-      <c r="D547" t="inlineStr"/>
+          <t>Net cash provided in financing activities</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E547" t="inlineStr">
         <is>
           <t>-</t>
@@ -62841,11 +62415,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G547" s="5" t="n">
-        <v>61.051</v>
-      </c>
-      <c r="H547" s="5" t="n">
-        <v>88.782</v>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I547" t="inlineStr">
         <is>
@@ -62857,20 +62435,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K547" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L547" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M547" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K547" s="5" t="n">
+        <v>109.692</v>
+      </c>
+      <c r="L547" s="5" t="n">
+        <v>350.516</v>
+      </c>
+      <c r="M547" s="5" t="n">
+        <v>445.846</v>
       </c>
       <c r="N547" t="inlineStr">
         <is>
@@ -62926,7 +62498,7 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Long-term incentive plan expense 21 10,233 26,422</t>
+          <t>Inventory write-down 8</t>
         </is>
       </c>
       <c r="D548" t="inlineStr"/>
@@ -62940,26 +62512,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G548" s="5" t="n">
-        <v>303.68</v>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H548" s="5" t="n">
-        <v>360.903</v>
-      </c>
-      <c r="I548" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J548" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K548" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5.628</v>
+      </c>
+      <c r="I548" s="5" t="n">
+        <v>2.058</v>
+      </c>
+      <c r="J548" s="5" t="n">
+        <v>60.639</v>
+      </c>
+      <c r="K548" s="5" t="n">
+        <v>3.388</v>
       </c>
       <c r="L548" t="inlineStr">
         <is>
@@ -63025,7 +62593,7 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>General and administrative expenses 25 (23,827) (22,167) Unrealized (gain) loss on foreign exchange</t>
+          <t>Net impairment expense 10</t>
         </is>
       </c>
       <c r="D549" t="inlineStr"/>
@@ -63039,11 +62607,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G549" s="5" t="n">
-        <v>1.647</v>
-      </c>
-      <c r="H549" s="5" t="n">
-        <v>-3.783</v>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I549" t="inlineStr">
         <is>
@@ -63055,15 +62627,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K549" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L549" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K549" s="5" t="n">
+        <v>95.30500000000001</v>
+      </c>
+      <c r="L549" s="5" t="n">
+        <v>12.27</v>
       </c>
       <c r="M549" t="inlineStr">
         <is>
@@ -63124,7 +62692,7 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Finance costs 26 (48,398) (42,389) Deferred income tax expense (recovery) 17</t>
+          <t>Loss on disposal of property, plant and equipment 10</t>
         </is>
       </c>
       <c r="D550" t="inlineStr"/>
@@ -63138,31 +62706,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G550" s="5" t="n">
-        <v>-13.567</v>
-      </c>
-      <c r="H550" s="5" t="n">
-        <v>38.506</v>
-      </c>
-      <c r="I550" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I550" s="5" t="n">
+        <v>0.482</v>
       </c>
       <c r="J550" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K550" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L550" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K550" s="5" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="L550" s="5" t="n">
+        <v>0.89</v>
       </c>
       <c r="M550" t="inlineStr">
         <is>
@@ -63218,12 +62784,12 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>Adjustments for items not affecting cash</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>Depreciation and amortization expense 27 (88,782) (61,051) Inventory write-down 8</t>
+          <t>Proceeds on sale of assets</t>
         </is>
       </c>
       <c r="D551" t="inlineStr"/>
@@ -63237,11 +62803,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G551" s="5" t="n">
-        <v>3.189</v>
-      </c>
-      <c r="H551" s="5" t="n">
-        <v>5.628</v>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I551" t="inlineStr">
         <is>
@@ -63253,15 +62823,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K551" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L551" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K551" s="5" t="n">
+        <v>3.478</v>
+      </c>
+      <c r="L551" s="5" t="n">
+        <v>0.08500000000000001</v>
       </c>
       <c r="M551" t="inlineStr">
         <is>
@@ -63317,12 +62883,12 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Adjustments for items not affecting cash</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>Net foreign currency gain (loss) on U.S. debt 23 11,134 (4,302) Loss on disposal of property, plant and equipment</t>
+          <t>Borrowings under credit facilities 14</t>
         </is>
       </c>
       <c r="D552" t="inlineStr"/>
@@ -63331,38 +62897,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F552" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F552" s="5" t="n">
+        <v>384</v>
       </c>
       <c r="G552" s="5" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="H552" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I552" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J552" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K552" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L552" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>325</v>
+      </c>
+      <c r="H552" s="5" t="n">
+        <v>752</v>
+      </c>
+      <c r="I552" s="5" t="n">
+        <v>1350</v>
+      </c>
+      <c r="J552" s="5" t="n">
+        <v>250</v>
+      </c>
+      <c r="K552" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="L552" s="5" t="n">
+        <v>1397.406</v>
       </c>
       <c r="M552" t="inlineStr">
         <is>
@@ -63418,12 +62972,12 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Adjustments for items not affecting cash</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Long-term incentive plan expense 21 (10,233) (26,422) Impairment expense 10</t>
+          <t>Repayments under credit facilities 14</t>
         </is>
       </c>
       <c r="D553" t="inlineStr"/>
@@ -63432,36 +62986,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F553" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F553" s="5" t="n">
+        <v>-303</v>
       </c>
       <c r="G553" s="5" t="n">
-        <v>24.012</v>
+        <v>-295</v>
       </c>
       <c r="H553" s="5" t="n">
-        <v>29.567</v>
-      </c>
-      <c r="I553" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J553" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K553" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L553" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-858</v>
+      </c>
+      <c r="I553" s="5" t="n">
+        <v>-1485</v>
+      </c>
+      <c r="J553" s="5" t="n">
+        <v>-160</v>
+      </c>
+      <c r="K553" s="5" t="n">
+        <v>-1020</v>
+      </c>
+      <c r="L553" s="5" t="n">
+        <v>-1532.406</v>
       </c>
       <c r="M553" t="inlineStr">
         <is>
@@ -63517,12 +63061,12 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>Adjustments for items not affecting cash</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>Decommissioning liability expenditures 16 (3,662) (2,754) Loss on disposal of property, plant and equipment</t>
+          <t>Proceeds from issuance of long-term debt 14</t>
         </is>
       </c>
       <c r="D554" t="inlineStr"/>
@@ -63531,38 +63075,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F554" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F554" s="5" t="n">
+        <v>154.099</v>
       </c>
       <c r="G554" s="5" t="n">
-        <v>-0.66</v>
-      </c>
-      <c r="H554" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I554" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J554" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>70</v>
+      </c>
+      <c r="H554" s="5" t="n">
+        <v>202.332</v>
+      </c>
+      <c r="I554" s="5" t="n">
+        <v>434.122</v>
+      </c>
+      <c r="J554" s="5" t="n">
+        <v>75</v>
       </c>
       <c r="K554" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L554" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L554" s="5" t="n">
+        <v>360</v>
       </c>
       <c r="M554" t="inlineStr">
         <is>
@@ -63618,50 +63152,50 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>Adjustments for items not affecting cash</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>Earnings before income tax</t>
-        </is>
-      </c>
-      <c r="D555" t="inlineStr"/>
+          <t>Repayment of long-term debt 14</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E555" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F555" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G555" s="5" t="n">
-        <v>122.677</v>
-      </c>
-      <c r="H555" s="5" t="n">
-        <v>171.23</v>
-      </c>
-      <c r="I555" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F555" s="5" t="n">
+        <v>-52.5</v>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I555" s="5" t="n">
+        <v>-52.5</v>
       </c>
       <c r="J555" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K555" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L555" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K555" s="5" t="n">
+        <v>-49.799</v>
+      </c>
+      <c r="L555" s="5" t="n">
+        <v>-97.73999999999999</v>
       </c>
       <c r="M555" t="inlineStr">
         <is>
@@ -63717,12 +63251,12 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>Income tax (expense) recovery 17 (40,629) 12,541 Business combination 6</t>
+          <t>Financing costs related to credit facilities/long-term debt 14</t>
         </is>
       </c>
       <c r="D556" t="inlineStr"/>
@@ -63741,28 +63275,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H556" s="5" t="n">
-        <v>-236.54</v>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I556" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J556" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K556" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L556" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J556" s="5" t="n">
+        <v>-2.07</v>
+      </c>
+      <c r="K556" s="5" t="n">
+        <v>-2.008</v>
+      </c>
+      <c r="L556" s="5" t="n">
+        <v>-2.238</v>
       </c>
       <c r="M556" t="inlineStr">
         <is>
@@ -63818,12 +63348,12 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>Adjustments for items not affecting cash</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>Net earnings 130,601 135,218 Asset acquisitions 10</t>
+          <t>Unrealized gain on derivative financial instruments 21</t>
         </is>
       </c>
       <c r="D557" t="inlineStr"/>
@@ -63837,26 +63367,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G557" s="5" t="n">
-        <v>-36.869</v>
-      </c>
-      <c r="H557" s="5" t="n">
-        <v>-44.203</v>
-      </c>
-      <c r="I557" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J557" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K557" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I557" s="5" t="n">
+        <v>-12.627</v>
+      </c>
+      <c r="J557" s="5" t="n">
+        <v>-114.329</v>
+      </c>
+      <c r="K557" s="5" t="n">
+        <v>-31.231</v>
       </c>
       <c r="L557" t="inlineStr">
         <is>
@@ -63917,19 +63445,15 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>Adjustments for items not affecting cash</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>Other comprehensive income – – Capital expenditures 10</t>
-        </is>
-      </c>
-      <c r="D558" t="inlineStr">
-        <is>
-          <t>CapitalExpenditure</t>
-        </is>
-      </c>
+          <t>Unrealized loss on foreign exchange</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr"/>
       <c r="E558" t="inlineStr">
         <is>
           <t>-</t>
@@ -63940,26 +63464,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G558" s="5" t="n">
-        <v>-133.911</v>
-      </c>
-      <c r="H558" s="5" t="n">
-        <v>-165.606</v>
-      </c>
-      <c r="I558" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J558" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K558" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I558" s="5" t="n">
+        <v>23.285</v>
+      </c>
+      <c r="J558" s="5" t="n">
+        <v>40.156</v>
+      </c>
+      <c r="K558" s="5" t="n">
+        <v>95.517</v>
       </c>
       <c r="L558" t="inlineStr">
         <is>
@@ -64025,7 +63547,7 @@
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>Total comprehensive income 130,601 135,218 Changes in non-cash working capital 29</t>
+          <t>Proceeds on sale of assets 10</t>
         </is>
       </c>
       <c r="D559" t="inlineStr"/>
@@ -64040,25 +63562,21 @@
         </is>
       </c>
       <c r="G559" s="5" t="n">
-        <v>2.897</v>
-      </c>
-      <c r="H559" s="5" t="n">
-        <v>6.148</v>
-      </c>
-      <c r="I559" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J559" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K559" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.142</v>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I559" s="5" t="n">
+        <v>9.811</v>
+      </c>
+      <c r="J559" s="5" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K559" s="5" t="n">
+        <v>3.478</v>
       </c>
       <c r="L559" t="inlineStr">
         <is>
@@ -64119,19 +63637,15 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>See accompanying notes to the audited consolidated financial statements. Net cash used in investing activities</t>
-        </is>
-      </c>
-      <c r="D560" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
+          <t>Proceeds from equity offering</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr"/>
       <c r="E560" t="inlineStr">
         <is>
           <t>-</t>
@@ -64142,21 +63656,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G560" s="5" t="n">
-        <v>-167.741</v>
-      </c>
-      <c r="H560" s="5" t="n">
-        <v>-440.201</v>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I560" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J560" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J560" s="5" t="n">
+        <v>318.047</v>
       </c>
       <c r="K560" t="inlineStr">
         <is>
@@ -64227,7 +63743,7 @@
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>Earnings per share Borrowings under credit facilities 14</t>
+          <t>Financing costs related to long-term debt 14</t>
         </is>
       </c>
       <c r="D561" t="inlineStr"/>
@@ -64236,26 +63752,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F561" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F561" s="5" t="n">
+        <v>-0.85</v>
       </c>
       <c r="G561" s="5" t="n">
-        <v>0.325</v>
+        <v>-0.144</v>
       </c>
       <c r="H561" s="5" t="n">
-        <v>0.752</v>
-      </c>
-      <c r="I561" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J561" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.21</v>
+      </c>
+      <c r="I561" s="5" t="n">
+        <v>-1.923</v>
+      </c>
+      <c r="J561" s="5" t="n">
+        <v>-2.07</v>
       </c>
       <c r="K561" t="inlineStr">
         <is>
@@ -64326,7 +63836,7 @@
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>Basic earnings per share 19 1.71 1.91 Repayments under credit facilities 14</t>
+          <t>Repayment of convertible debenture</t>
         </is>
       </c>
       <c r="D562" t="inlineStr"/>
@@ -64340,16 +63850,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G562" s="5" t="n">
-        <v>-0.295</v>
-      </c>
-      <c r="H562" s="5" t="n">
-        <v>-0.858</v>
-      </c>
-      <c r="I562" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I562" s="5" t="n">
+        <v>-0.039</v>
       </c>
       <c r="J562" t="inlineStr">
         <is>
@@ -64425,7 +63937,7 @@
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>Diluted earnings per share 19 1.71 1.90 Proceeds from issuance of long-term debt 14</t>
+          <t>Cash, at the start of the period</t>
         </is>
       </c>
       <c r="D563" t="inlineStr"/>
@@ -64440,20 +63952,16 @@
         </is>
       </c>
       <c r="G563" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>14.977</v>
       </c>
       <c r="H563" s="5" t="n">
-        <v>0.202332</v>
-      </c>
-      <c r="I563" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J563" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>21.813</v>
+      </c>
+      <c r="I563" s="5" t="n">
+        <v>0.518</v>
+      </c>
+      <c r="J563" s="5" t="n">
+        <v>186.651</v>
       </c>
       <c r="K563" t="inlineStr">
         <is>
@@ -64524,10 +64032,14 @@
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of shares related to DRIP</t>
-        </is>
-      </c>
-      <c r="D564" t="inlineStr"/>
+          <t>Cash, at the end of the period</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E564" t="inlineStr">
         <is>
           <t>-</t>
@@ -64539,20 +64051,16 @@
         </is>
       </c>
       <c r="G564" s="5" t="n">
-        <v>31.227</v>
+        <v>21.813</v>
       </c>
       <c r="H564" s="5" t="n">
-        <v>47.901</v>
-      </c>
-      <c r="I564" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J564" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.518</v>
+      </c>
+      <c r="I564" s="5" t="n">
+        <v>186.651</v>
+      </c>
+      <c r="J564" s="5" t="n">
+        <v>11.309</v>
       </c>
       <c r="K564" t="inlineStr">
         <is>
@@ -64618,17 +64126,17 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Adjustments for items not affecting cash</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>Net cash provided by / (used in) financing activities</t>
+          <t>Depreciation and amortization expense 27</t>
         </is>
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E565" t="inlineStr">
@@ -64636,21 +64144,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F565" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F565" s="5" t="n">
+        <v>53.342</v>
       </c>
       <c r="G565" s="5" t="n">
-        <v>-3.447</v>
+        <v>61.051</v>
       </c>
       <c r="H565" s="5" t="n">
-        <v>181.322</v>
-      </c>
-      <c r="I565" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>88.782</v>
+      </c>
+      <c r="I565" s="5" t="n">
+        <v>102.425</v>
       </c>
       <c r="J565" t="inlineStr">
         <is>
@@ -64721,12 +64225,12 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>Adjustments for items not affecting cash</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>Unrealized loss on the settlement of convertible debenture derivative liability 22</t>
+          <t>Business combination 6</t>
         </is>
       </c>
       <c r="D566" t="inlineStr"/>
@@ -64735,18 +64239,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F566" s="5" t="n">
-        <v>24.894</v>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G566" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H566" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H566" s="5" t="n">
+        <v>-236.54</v>
       </c>
       <c r="I566" t="inlineStr">
         <is>
@@ -64822,12 +64326,12 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>Adjustments for items not affecting cash</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>Deferred income tax (recovery) expense 17</t>
+          <t>Asset acquisitions 10</t>
         </is>
       </c>
       <c r="D567" t="inlineStr"/>
@@ -64836,21 +64340,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F567" s="5" t="n">
-        <v>6.205</v>
-      </c>
-      <c r="G567" s="5" t="n">
-        <v>-13.567</v>
-      </c>
-      <c r="H567" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I567" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H567" s="5" t="n">
+        <v>-44.203</v>
+      </c>
+      <c r="I567" s="5" t="n">
+        <v>-31.878</v>
       </c>
       <c r="J567" t="inlineStr">
         <is>
@@ -64921,12 +64425,12 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>Adjustments for items not affecting cash</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>Loss on disposal of property, plant and equipment</t>
+          <t>Repayment of convertible debenture 15</t>
         </is>
       </c>
       <c r="D568" t="inlineStr"/>
@@ -64941,17 +64445,15 @@
         </is>
       </c>
       <c r="G568" s="5" t="n">
-        <v>0.66</v>
+        <v>-0.043</v>
       </c>
       <c r="H568" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I568" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I568" s="5" t="n">
+        <v>-0.039</v>
       </c>
       <c r="J568" t="inlineStr">
         <is>
@@ -65022,32 +64524,34 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>Cash provided by (used in)</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>Business combination 9</t>
-        </is>
-      </c>
-      <c r="D569" t="inlineStr"/>
+          <t>(Thousands of Canadian dollars, except share information) Note $ $ Net earnings</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E569" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F569" s="5" t="n">
-        <v>-123.708</v>
-      </c>
-      <c r="G569" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H569" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G569" s="5" t="n">
+        <v>135.218</v>
+      </c>
+      <c r="H569" s="5" t="n">
+        <v>130.601</v>
       </c>
       <c r="I569" t="inlineStr">
         <is>
@@ -65123,12 +64627,12 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Adjustments for items not affecting cash</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of shares/trust units 18</t>
+          <t>Operating revenues 30 2,942,277 2,569,158 Finance costs 26</t>
         </is>
       </c>
       <c r="D570" t="inlineStr"/>
@@ -65137,16 +64641,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F570" s="5" t="n">
-        <v>38.714</v>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G570" s="5" t="n">
-        <v>31.227</v>
-      </c>
-      <c r="H570" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>7.501</v>
+      </c>
+      <c r="H570" s="5" t="n">
+        <v>8.952999999999999</v>
       </c>
       <c r="I570" t="inlineStr">
         <is>
@@ -65222,30 +64726,34 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Adjustments for items not affecting cash</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Dividends/distributions paid to shareholders/unitholders 20</t>
-        </is>
-      </c>
-      <c r="D571" t="inlineStr"/>
+          <t>Operating expenses 30 (2,581,374) (2,265,478) Depreciation and amortization expense 27</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E571" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F571" s="5" t="n">
-        <v>-122.245</v>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G571" s="5" t="n">
-        <v>-134.487</v>
-      </c>
-      <c r="H571" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>61.051</v>
+      </c>
+      <c r="H571" s="5" t="n">
+        <v>88.782</v>
       </c>
       <c r="I571" t="inlineStr">
         <is>
@@ -65321,34 +64829,30 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Adjustments for items not affecting cash</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Net cash (used in)/provided by financing activities</t>
-        </is>
-      </c>
-      <c r="D572" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
+          <t>Long-term incentive plan expense 21 10,233 26,422</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr"/>
       <c r="E572" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F572" s="5" t="n">
-        <v>98.218</v>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G572" s="5" t="n">
-        <v>-3.447</v>
-      </c>
-      <c r="H572" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>303.68</v>
+      </c>
+      <c r="H572" s="5" t="n">
+        <v>360.903</v>
       </c>
       <c r="I572" t="inlineStr">
         <is>
@@ -65424,12 +64928,12 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Adjustments for items not affecting cash</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents (bank indebtedness) at the start of the period</t>
+          <t>General and administrative expenses 25 (23,827) (22,167) Unrealized (gain) loss on foreign exchange</t>
         </is>
       </c>
       <c r="D573" t="inlineStr"/>
@@ -65438,16 +64942,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F573" s="5" t="n">
-        <v>-0.777</v>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G573" s="5" t="n">
-        <v>14.977</v>
-      </c>
-      <c r="H573" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.647</v>
+      </c>
+      <c r="H573" s="5" t="n">
+        <v>-3.783</v>
       </c>
       <c r="I573" t="inlineStr">
         <is>
@@ -65523,30 +65027,34 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Adjustments for items not affecting cash</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents at the end of the period</t>
-        </is>
-      </c>
-      <c r="D574" t="inlineStr"/>
+          <t>Finance costs 26 (48,398) (42,389) Deferred income tax expense (recovery) 17</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E574" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F574" s="5" t="n">
-        <v>14.977</v>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G574" s="5" t="n">
-        <v>21.813</v>
-      </c>
-      <c r="H574" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-13.567</v>
+      </c>
+      <c r="H574" s="5" t="n">
+        <v>38.506</v>
       </c>
       <c r="I574" t="inlineStr">
         <is>
@@ -65622,34 +65130,30 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Adjustments for items not affecting cash</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>Net earnings</t>
-        </is>
-      </c>
-      <c r="D575" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E575" s="5" t="n">
-        <v>150.324</v>
-      </c>
-      <c r="F575" s="5" t="n">
-        <v>125.046</v>
-      </c>
-      <c r="G575" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H575" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Depreciation and amortization expense 27 (88,782) (61,051) Inventory write-down 8</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr"/>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G575" s="5" t="n">
+        <v>3.189</v>
+      </c>
+      <c r="H575" s="5" t="n">
+        <v>5.628</v>
       </c>
       <c r="I575" t="inlineStr">
         <is>
@@ -65725,29 +65229,27 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Adjustments for items not affecting cash</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>Depreciation and amortization</t>
-        </is>
-      </c>
-      <c r="D576" t="inlineStr">
-        <is>
-          <t>DepreciationAndAmortization</t>
-        </is>
-      </c>
-      <c r="E576" s="5" t="n">
-        <v>42.07</v>
-      </c>
-      <c r="F576" s="5" t="n">
-        <v>44.955</v>
-      </c>
-      <c r="G576" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net foreign currency gain (loss) on U.S. debt 23 11,134 (4,302) Loss on disposal of property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr"/>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G576" s="5" t="n">
+        <v>0.66</v>
       </c>
       <c r="H576" t="inlineStr">
         <is>
@@ -65828,30 +65330,30 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Adjustments for items not affecting cash</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>Accretion expense</t>
+          <t>Long-term incentive plan expense 21 (10,233) (26,422) Impairment expense 10</t>
         </is>
       </c>
       <c r="D577" t="inlineStr"/>
-      <c r="E577" s="5" t="n">
-        <v>3.362</v>
-      </c>
-      <c r="F577" s="5" t="n">
-        <v>5.019</v>
-      </c>
-      <c r="G577" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H577" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G577" s="5" t="n">
+        <v>24.012</v>
+      </c>
+      <c r="H577" s="5" t="n">
+        <v>29.567</v>
       </c>
       <c r="I577" t="inlineStr">
         <is>
@@ -65927,25 +65429,27 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Accretion of financing costs and debt discount related</t>
+          <t>Adjustments for items not affecting cash</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>Accretion of financing costs and debt discount related to convertible debentures and long-term debt</t>
+          <t>Decommissioning liability expenditures 16 (3,662) (2,754) Loss on disposal of property, plant and equipment</t>
         </is>
       </c>
       <c r="D578" t="inlineStr"/>
-      <c r="E578" s="5" t="n">
-        <v>1.684</v>
-      </c>
-      <c r="F578" s="5" t="n">
-        <v>1.295</v>
-      </c>
-      <c r="G578" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G578" s="5" t="n">
+        <v>-0.66</v>
       </c>
       <c r="H578" t="inlineStr">
         <is>
@@ -66026,30 +65530,30 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>Accretion of financing costs and debt discount related</t>
+          <t>Adjustments for items not affecting cash</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Impairment expense (note 6)</t>
+          <t>Earnings before income tax</t>
         </is>
       </c>
       <c r="D579" t="inlineStr"/>
-      <c r="E579" s="5" t="n">
-        <v>2.778</v>
-      </c>
-      <c r="F579" s="5" t="n">
-        <v>3.617</v>
-      </c>
-      <c r="G579" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H579" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G579" s="5" t="n">
+        <v>122.677</v>
+      </c>
+      <c r="H579" s="5" t="n">
+        <v>171.23</v>
       </c>
       <c r="I579" t="inlineStr">
         <is>
@@ -66125,12 +65629,12 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>Accretion of financing costs and debt discount related</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Inventory write-down (note 4)</t>
+          <t>Income tax (expense) recovery 17 (40,629) 12,541 Business combination 6</t>
         </is>
       </c>
       <c r="D580" t="inlineStr"/>
@@ -66139,18 +65643,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F580" s="5" t="n">
-        <v>7.9</v>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G580" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H580" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H580" s="5" t="n">
+        <v>-236.54</v>
       </c>
       <c r="I580" t="inlineStr">
         <is>
@@ -66226,32 +65730,30 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>Accretion of financing costs and debt discount related</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>Loss on disposal of assets</t>
+          <t>Net earnings 130,601 135,218 Asset acquisitions 10</t>
         </is>
       </c>
       <c r="D581" t="inlineStr"/>
-      <c r="E581" s="5" t="n">
-        <v>4.632</v>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F581" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G581" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H581" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G581" s="5" t="n">
+        <v>-36.869</v>
+      </c>
+      <c r="H581" s="5" t="n">
+        <v>-44.203</v>
       </c>
       <c r="I581" t="inlineStr">
         <is>
@@ -66327,30 +65829,34 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Accretion of financing costs and debt discount related</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>Unrealized loss on financial instruments (note 17)</t>
-        </is>
-      </c>
-      <c r="D582" t="inlineStr"/>
-      <c r="E582" s="5" t="n">
-        <v>61.468</v>
-      </c>
-      <c r="F582" s="5" t="n">
-        <v>25.797</v>
-      </c>
-      <c r="G582" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H582" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Other comprehensive income – – Capital expenditures 10</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>CapitalExpenditure</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G582" s="5" t="n">
+        <v>-133.911</v>
+      </c>
+      <c r="H582" s="5" t="n">
+        <v>-165.606</v>
       </c>
       <c r="I582" t="inlineStr">
         <is>
@@ -66426,30 +65932,30 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Accretion of financing costs and debt discount related</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>Unrealized gain on foreign exchange</t>
+          <t>Total comprehensive income 130,601 135,218 Changes in non-cash working capital 29</t>
         </is>
       </c>
       <c r="D583" t="inlineStr"/>
-      <c r="E583" s="5" t="n">
-        <v>-2.248</v>
-      </c>
-      <c r="F583" s="5" t="n">
-        <v>-2.984</v>
-      </c>
-      <c r="G583" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H583" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G583" s="5" t="n">
+        <v>2.897</v>
+      </c>
+      <c r="H583" s="5" t="n">
+        <v>6.148</v>
       </c>
       <c r="I583" t="inlineStr">
         <is>
@@ -66525,30 +66031,34 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>Accretion of financing costs and debt discount related</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>Long-term incentive plan expense (note 16)</t>
-        </is>
-      </c>
-      <c r="D584" t="inlineStr"/>
-      <c r="E584" s="5" t="n">
-        <v>12.687</v>
-      </c>
-      <c r="F584" s="5" t="n">
-        <v>18.225</v>
-      </c>
-      <c r="G584" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H584" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>See accompanying notes to the audited consolidated financial statements. Net cash used in investing activities</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G584" s="5" t="n">
+        <v>-167.741</v>
+      </c>
+      <c r="H584" s="5" t="n">
+        <v>-440.201</v>
       </c>
       <c r="I584" t="inlineStr">
         <is>
@@ -66624,30 +66134,30 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>Accretion of financing costs and debt discount related</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>Future income tax expense (recovery) (note 12)</t>
+          <t>Earnings per share Borrowings under credit facilities 14</t>
         </is>
       </c>
       <c r="D585" t="inlineStr"/>
-      <c r="E585" s="5" t="n">
-        <v>-0.54</v>
-      </c>
-      <c r="F585" s="5" t="n">
-        <v>8.157</v>
-      </c>
-      <c r="G585" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H585" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G585" s="5" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="H585" s="5" t="n">
+        <v>0.752</v>
       </c>
       <c r="I585" t="inlineStr">
         <is>
@@ -66723,30 +66233,30 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>Accretion of financing costs and debt discount related</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>Asset retirement obligation expenditures (note 11)</t>
+          <t>Basic earnings per share 19 1.71 1.91 Repayments under credit facilities 14</t>
         </is>
       </c>
       <c r="D586" t="inlineStr"/>
-      <c r="E586" s="5" t="n">
-        <v>-2.271</v>
-      </c>
-      <c r="F586" s="5" t="n">
-        <v>-0.878</v>
-      </c>
-      <c r="G586" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H586" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G586" s="5" t="n">
+        <v>-0.295</v>
+      </c>
+      <c r="H586" s="5" t="n">
+        <v>-0.858</v>
       </c>
       <c r="I586" t="inlineStr">
         <is>
@@ -66822,34 +66332,30 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>Accretion of financing costs and debt discount related</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital (note 20)</t>
-        </is>
-      </c>
-      <c r="D587" t="inlineStr">
-        <is>
-          <t>ChangeInWorkingCapital</t>
-        </is>
-      </c>
-      <c r="E587" s="5" t="n">
-        <v>39.238</v>
-      </c>
-      <c r="F587" s="5" t="n">
-        <v>-82.41500000000001</v>
-      </c>
-      <c r="G587" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H587" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Diluted earnings per share 19 1.71 1.90 Proceeds from issuance of long-term debt 14</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr"/>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G587" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H587" s="5" t="n">
+        <v>0.202332</v>
       </c>
       <c r="I587" t="inlineStr">
         <is>
@@ -66925,30 +66431,30 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>Accretion of financing costs and debt discount related</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>Accretion of financing costs and debt discount related total</t>
+          <t>Proceeds from issuance of shares related to DRIP</t>
         </is>
       </c>
       <c r="D588" t="inlineStr"/>
-      <c r="E588" s="5" t="n">
-        <v>313.184</v>
-      </c>
-      <c r="F588" s="5" t="n">
-        <v>153.734</v>
-      </c>
-      <c r="G588" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H588" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G588" s="5" t="n">
+        <v>31.227</v>
+      </c>
+      <c r="H588" s="5" t="n">
+        <v>47.901</v>
       </c>
       <c r="I588" t="inlineStr">
         <is>
@@ -67024,32 +66530,34 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>Business combination (note 5)</t>
-        </is>
-      </c>
-      <c r="D589" t="inlineStr"/>
+          <t>Net cash provided by / (used in) financing activities</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E589" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F589" s="5" t="n">
-        <v>-123.708</v>
-      </c>
-      <c r="G589" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H589" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G589" s="5" t="n">
+        <v>-3.447</v>
+      </c>
+      <c r="H589" s="5" t="n">
+        <v>181.322</v>
       </c>
       <c r="I589" t="inlineStr">
         <is>
@@ -67125,24 +66633,22 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Adjustments for items not affecting cash</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>Capital expenditures</t>
-        </is>
-      </c>
-      <c r="D590" t="inlineStr">
-        <is>
-          <t>CapitalExpenditure</t>
-        </is>
-      </c>
-      <c r="E590" s="5" t="n">
-        <v>-100.056</v>
+          <t>Unrealized loss on the settlement of convertible debenture derivative liability 22</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr"/>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F590" s="5" t="n">
-        <v>-120.881</v>
+        <v>24.894</v>
       </c>
       <c r="G590" t="inlineStr">
         <is>
@@ -67228,27 +66734,25 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Adjustments for items not affecting cash</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>Proceeds on sale of assets</t>
+          <t>Deferred income tax (recovery) expense 17</t>
         </is>
       </c>
       <c r="D591" t="inlineStr"/>
-      <c r="E591" s="5" t="n">
-        <v>3.777</v>
-      </c>
-      <c r="F591" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G591" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F591" s="5" t="n">
+        <v>6.205</v>
+      </c>
+      <c r="G591" s="5" t="n">
+        <v>-13.567</v>
       </c>
       <c r="H591" t="inlineStr">
         <is>
@@ -67329,29 +66833,27 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Adjustments for items not affecting cash</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital (note 20)</t>
-        </is>
-      </c>
-      <c r="D592" t="inlineStr">
-        <is>
-          <t>ChangeInWorkingCapital</t>
-        </is>
-      </c>
-      <c r="E592" s="5" t="n">
-        <v>-10.181</v>
-      </c>
-      <c r="F592" s="5" t="n">
-        <v>8.391</v>
-      </c>
-      <c r="G592" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Loss on disposal of property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr"/>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G592" s="5" t="n">
+        <v>0.66</v>
       </c>
       <c r="H592" t="inlineStr">
         <is>
@@ -67432,24 +66934,22 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>Investing activities total</t>
-        </is>
-      </c>
-      <c r="D593" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
-      <c r="E593" s="5" t="n">
-        <v>-106.46</v>
+          <t>Business combination 9</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr"/>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F593" s="5" t="n">
-        <v>-236.198</v>
+        <v>-123.708</v>
       </c>
       <c r="G593" t="inlineStr">
         <is>
@@ -67535,29 +67035,25 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>Increase (decrease) of credit facilities (note 9)</t>
-        </is>
-      </c>
-      <c r="D594" t="inlineStr">
-        <is>
-          <t>NetIssuancePaymentsOfDebt</t>
-        </is>
-      </c>
-      <c r="E594" s="5" t="n">
-        <v>-119</v>
+          <t>Proceeds from issuance of shares/trust units 18</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr"/>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F594" s="5" t="n">
-        <v>81</v>
-      </c>
-      <c r="G594" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>38.714</v>
+      </c>
+      <c r="G594" s="5" t="n">
+        <v>31.227</v>
       </c>
       <c r="H594" t="inlineStr">
         <is>
@@ -67638,29 +67134,25 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>Repayment of long-term debt (note 9)</t>
-        </is>
-      </c>
-      <c r="D595" t="inlineStr">
-        <is>
-          <t>RepaymentOfDebt</t>
-        </is>
-      </c>
-      <c r="E595" s="5" t="n">
-        <v>-90</v>
+          <t>Dividends/distributions paid to shareholders/unitholders 20</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr"/>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F595" s="5" t="n">
-        <v>-52.5</v>
-      </c>
-      <c r="G595" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-122.245</v>
+      </c>
+      <c r="G595" s="5" t="n">
+        <v>-134.487</v>
       </c>
       <c r="H595" t="inlineStr">
         <is>
@@ -67741,25 +67233,29 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>Issuance of long-term debt (note 9)</t>
-        </is>
-      </c>
-      <c r="D596" t="inlineStr"/>
-      <c r="E596" s="5" t="n">
-        <v>94.7</v>
+          <t>Net cash (used in)/provided by financing activities</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F596" s="5" t="n">
-        <v>154.099</v>
-      </c>
-      <c r="G596" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>98.218</v>
+      </c>
+      <c r="G596" s="5" t="n">
+        <v>-3.447</v>
       </c>
       <c r="H596" t="inlineStr">
         <is>
@@ -67840,25 +67336,25 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>Financing costs related to long-term debt (note 9)</t>
+          <t>Cash and cash equivalents (bank indebtedness) at the start of the period</t>
         </is>
       </c>
       <c r="D597" t="inlineStr"/>
-      <c r="E597" s="5" t="n">
-        <v>-0.527</v>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F597" s="5" t="n">
-        <v>-0.85</v>
-      </c>
-      <c r="G597" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.777</v>
+      </c>
+      <c r="G597" s="5" t="n">
+        <v>14.977</v>
       </c>
       <c r="H597" t="inlineStr">
         <is>
@@ -67939,25 +67435,25 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>Issuance of trust units (note 13)</t>
+          <t>Cash and cash equivalents at the end of the period</t>
         </is>
       </c>
       <c r="D598" t="inlineStr"/>
-      <c r="E598" s="5" t="n">
-        <v>36.186</v>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F598" s="5" t="n">
-        <v>38.714</v>
-      </c>
-      <c r="G598" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>14.977</v>
+      </c>
+      <c r="G598" s="5" t="n">
+        <v>21.813</v>
       </c>
       <c r="H598" t="inlineStr">
         <is>
@@ -68038,20 +67534,24 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>Distributions paid to unitholders (note 15)</t>
-        </is>
-      </c>
-      <c r="D599" t="inlineStr"/>
+          <t>Net earnings</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E599" s="5" t="n">
-        <v>-128.973</v>
+        <v>150.324</v>
       </c>
       <c r="F599" s="5" t="n">
-        <v>-122.245</v>
+        <v>125.046</v>
       </c>
       <c r="G599" t="inlineStr">
         <is>
@@ -68137,24 +67637,24 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>Financing activities total</t>
+          <t>Depreciation and amortization</t>
         </is>
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E600" s="5" t="n">
-        <v>-207.614</v>
+        <v>42.07</v>
       </c>
       <c r="F600" s="5" t="n">
-        <v>98.218</v>
+        <v>44.955</v>
       </c>
       <c r="G600" t="inlineStr">
         <is>
@@ -68240,20 +67740,24 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>Net cash inflow (outflow)</t>
-        </is>
-      </c>
-      <c r="D601" t="inlineStr"/>
+          <t>Accretion expense</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E601" s="5" t="n">
-        <v>-0.89</v>
+        <v>3.362</v>
       </c>
       <c r="F601" s="5" t="n">
-        <v>15.754</v>
+        <v>5.019</v>
       </c>
       <c r="G601" t="inlineStr">
         <is>
@@ -68339,24 +67843,20 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Accretion of financing costs and debt discount related</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>(Bank indebtedness) cash, beginning of year</t>
-        </is>
-      </c>
-      <c r="D602" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Accretion of financing costs and debt discount related to convertible debentures and long-term debt</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr"/>
       <c r="E602" s="5" t="n">
-        <v>0.113</v>
+        <v>1.684</v>
       </c>
       <c r="F602" s="5" t="n">
-        <v>-0.777</v>
+        <v>1.295</v>
       </c>
       <c r="G602" t="inlineStr">
         <is>
@@ -68442,92 +67942,2508 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Accretion of financing costs and debt discount related</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>Cash (bank indebtedness), end of year</t>
+          <t>Impairment expense (note 6)</t>
         </is>
       </c>
       <c r="D603" t="inlineStr"/>
       <c r="E603" s="5" t="n">
+        <v>2.778</v>
+      </c>
+      <c r="F603" s="5" t="n">
+        <v>3.617</v>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J603" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L603" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M603" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N603" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O603" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P603" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q603" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R603" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S603" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T603" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U603" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>Accretion of financing costs and debt discount related</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>Inventory write-down (note 4)</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr"/>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F604" s="5" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J604" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L604" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M604" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N604" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O604" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P604" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q604" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R604" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S604" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T604" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U604" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>Accretion of financing costs and debt discount related</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>Loss on disposal of assets</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr"/>
+      <c r="E605" s="5" t="n">
+        <v>4.632</v>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J605" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L605" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M605" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N605" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O605" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P605" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q605" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R605" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S605" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T605" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U605" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>Accretion of financing costs and debt discount related</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>Unrealized loss on financial instruments (note 17)</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr"/>
+      <c r="E606" s="5" t="n">
+        <v>61.468</v>
+      </c>
+      <c r="F606" s="5" t="n">
+        <v>25.797</v>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J606" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L606" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M606" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N606" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O606" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P606" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q606" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R606" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S606" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T606" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U606" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>Accretion of financing costs and debt discount related</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>Unrealized gain on foreign exchange</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr"/>
+      <c r="E607" s="5" t="n">
+        <v>-2.248</v>
+      </c>
+      <c r="F607" s="5" t="n">
+        <v>-2.984</v>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J607" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L607" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M607" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N607" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O607" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P607" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q607" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R607" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S607" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T607" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U607" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>Accretion of financing costs and debt discount related</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>Long-term incentive plan expense (note 16)</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr"/>
+      <c r="E608" s="5" t="n">
+        <v>12.687</v>
+      </c>
+      <c r="F608" s="5" t="n">
+        <v>18.225</v>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J608" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L608" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M608" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N608" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O608" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P608" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q608" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R608" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S608" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T608" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U608" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>Accretion of financing costs and debt discount related</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>Future income tax expense (recovery) (note 12)</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr"/>
+      <c r="E609" s="5" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="F609" s="5" t="n">
+        <v>8.157</v>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J609" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L609" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M609" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N609" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O609" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P609" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q609" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R609" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S609" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T609" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U609" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>Accretion of financing costs and debt discount related</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>Asset retirement obligation expenditures (note 11)</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr"/>
+      <c r="E610" s="5" t="n">
+        <v>-2.271</v>
+      </c>
+      <c r="F610" s="5" t="n">
+        <v>-0.878</v>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I610" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J610" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L610" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M610" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N610" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O610" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P610" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q610" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R610" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S610" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T610" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U610" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>Accretion of financing costs and debt discount related</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>Changes in non-cash working capital (note 20)</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
+      <c r="E611" s="5" t="n">
+        <v>39.238</v>
+      </c>
+      <c r="F611" s="5" t="n">
+        <v>-82.41500000000001</v>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J611" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L611" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M611" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N611" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O611" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P611" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q611" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R611" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S611" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T611" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U611" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>Accretion of financing costs and debt discount related</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>Accretion of financing costs and debt discount related total</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr"/>
+      <c r="E612" s="5" t="n">
+        <v>313.184</v>
+      </c>
+      <c r="F612" s="5" t="n">
+        <v>153.734</v>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J612" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L612" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M612" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N612" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O612" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P612" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q612" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R612" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S612" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T612" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U612" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>Investing activities</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>Business combination (note 5)</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr"/>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F613" s="5" t="n">
+        <v>-123.708</v>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J613" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L613" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M613" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N613" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O613" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P613" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q613" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R613" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S613" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T613" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U613" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>Investing activities</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>Capital expenditures</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>CapitalExpenditure</t>
+        </is>
+      </c>
+      <c r="E614" s="5" t="n">
+        <v>-100.056</v>
+      </c>
+      <c r="F614" s="5" t="n">
+        <v>-120.881</v>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J614" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L614" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M614" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N614" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O614" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P614" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q614" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R614" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S614" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T614" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U614" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>Investing activities</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>Proceeds on sale of assets</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr"/>
+      <c r="E615" s="5" t="n">
+        <v>3.777</v>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J615" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L615" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M615" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N615" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O615" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P615" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q615" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R615" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S615" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T615" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U615" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>Investing activities</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>Changes in non-cash working capital (note 20)</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
+      <c r="E616" s="5" t="n">
+        <v>-10.181</v>
+      </c>
+      <c r="F616" s="5" t="n">
+        <v>8.391</v>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J616" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L616" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M616" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N616" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O616" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P616" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q616" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R616" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S616" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T616" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U616" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>Investing activities</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>Investing activities total</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E617" s="5" t="n">
+        <v>-106.46</v>
+      </c>
+      <c r="F617" s="5" t="n">
+        <v>-236.198</v>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J617" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L617" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M617" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N617" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O617" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P617" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q617" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R617" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S617" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T617" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U617" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>Increase (decrease) of credit facilities (note 9)</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>NetIssuancePaymentsOfDebt</t>
+        </is>
+      </c>
+      <c r="E618" s="5" t="n">
+        <v>-119</v>
+      </c>
+      <c r="F618" s="5" t="n">
+        <v>81</v>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J618" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L618" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M618" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N618" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O618" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P618" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q618" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R618" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S618" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T618" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U618" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>Repayment of long-term debt (note 9)</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
+      <c r="E619" s="5" t="n">
+        <v>-90</v>
+      </c>
+      <c r="F619" s="5" t="n">
+        <v>-52.5</v>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J619" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L619" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M619" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N619" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O619" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P619" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q619" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R619" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S619" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T619" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U619" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>Issuance of long-term debt (note 9)</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr"/>
+      <c r="E620" s="5" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="F620" s="5" t="n">
+        <v>154.099</v>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H620" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J620" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L620" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M620" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N620" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O620" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P620" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q620" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R620" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S620" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T620" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U620" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>Financing costs related to long-term debt (note 9)</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr"/>
+      <c r="E621" s="5" t="n">
+        <v>-0.527</v>
+      </c>
+      <c r="F621" s="5" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J621" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L621" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M621" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N621" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O621" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P621" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q621" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R621" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S621" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T621" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U621" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>Issuance of trust units (note 13)</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr"/>
+      <c r="E622" s="5" t="n">
+        <v>36.186</v>
+      </c>
+      <c r="F622" s="5" t="n">
+        <v>38.714</v>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J622" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L622" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M622" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N622" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O622" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P622" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q622" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R622" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S622" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T622" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U622" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>Distributions paid to unitholders (note 15)</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr"/>
+      <c r="E623" s="5" t="n">
+        <v>-128.973</v>
+      </c>
+      <c r="F623" s="5" t="n">
+        <v>-122.245</v>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J623" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L623" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M623" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N623" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O623" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P623" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q623" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R623" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S623" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T623" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U623" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>Financing activities total</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E624" s="5" t="n">
+        <v>-207.614</v>
+      </c>
+      <c r="F624" s="5" t="n">
+        <v>98.218</v>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J624" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L624" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M624" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N624" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O624" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P624" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q624" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R624" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S624" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T624" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U624" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>Net cash inflow (outflow)</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr"/>
+      <c r="E625" s="5" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="F625" s="5" t="n">
+        <v>15.754</v>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J625" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L625" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M625" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N625" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O625" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P625" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q625" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R625" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S625" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T625" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U625" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>(Bank indebtedness) cash, beginning of year</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E626" s="5" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="F626" s="5" t="n">
         <v>-0.777</v>
       </c>
-      <c r="F603" s="5" t="n">
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I626" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J626" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L626" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M626" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N626" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O626" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P626" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q626" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R626" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S626" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T626" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U626" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>Cash (bank indebtedness), end of year</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr"/>
+      <c r="E627" s="5" t="n">
+        <v>-0.777</v>
+      </c>
+      <c r="F627" s="5" t="n">
         <v>14.977</v>
       </c>
-      <c r="G603" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H603" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I603" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J603" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K603" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L603" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M603" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N603" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O603" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P603" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q603" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R603" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S603" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T603" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U603" t="inlineStr">
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J627" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L627" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M627" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N627" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O627" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P627" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q627" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R627" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S627" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T627" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U627" t="inlineStr">
         <is>
           <t>-</t>
         </is>
